--- a/tables_filled/22b5da6f-d542-421f-b00b-8d360f06d0b0.xlsx
+++ b/tables_filled/22b5da6f-d542-421f-b00b-8d360f06d0b0.xlsx
@@ -20,6 +20,1283 @@
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
+  <si>
+    <t>a)    Projektleiter*in</t>
+  </si>
+  <si>
+    <t>Anforderungen der Auftraggeberin gemäß Auftragsbekanntmachung III.1.3. Technische und berufliche Leistungsfähigkeit (2) Eignung Personal</t>
+  </si>
+  <si>
+    <t>- Sanierungs- und/oder Modernisierungsmaßnahme für ein mehrgeschossiges Hochbauprojekt</t>
+  </si>
+  <si>
+    <t>- Realisierung innerhalb der Europäischen Union (EU) oder der Schweiz</t>
+  </si>
+  <si>
+    <t>Allgemeine Mindeststandards, die mit jeder persönlichen Referenz nachgewiesen werden müssen:</t>
+  </si>
+  <si>
+    <t>Lfd. Referenz-Nr.</t>
+  </si>
+  <si>
+    <t>Bietername</t>
+  </si>
+  <si>
+    <t>Vorname, Name</t>
+  </si>
+  <si>
+    <t>Referenzbezeichnung</t>
+  </si>
+  <si>
+    <t>Bauherr / Referenzgeber 
+(Name, Anschrift, Kontaktdaten):</t>
+  </si>
+  <si>
+    <t>Referenz 1</t>
+  </si>
+  <si>
+    <t>Referenz 2</t>
+  </si>
+  <si>
+    <t>Angabe Leistungsphasen in Projektleitungsfunktion:</t>
+  </si>
+  <si>
+    <t>Anzahl Geschosse mit Sanierung/Modernisierung:</t>
+  </si>
+  <si>
+    <t>Angabe Objekttyp gem. Anlage 10.2 HOAI:</t>
+  </si>
+  <si>
+    <t>Ort/Land:</t>
+  </si>
+  <si>
+    <t>Übernahme aus Abfrage Mindeststandards</t>
+  </si>
+  <si>
+    <t>Angabe der Brandschutzaßnahmen</t>
+  </si>
+  <si>
+    <t>Angabe der Schadstoffsanierung</t>
+  </si>
+  <si>
+    <t>Angabe zur Strangsanierung</t>
+  </si>
+  <si>
+    <t>- von mindestens 8 Jahren nach Erwerb des Ausbildungsabschlusses</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Das Referenzobjekt unterfällt zudem einer der folgenden Kategorien/Objekttypen der Objektliste Anlage 10.2 der HOAI ab Honorarzone III: "Gesundheit/Betreuung", "Wohnen", "Studentenhäuser", "Hotels" bzw. "Bauten für den Strafvollzug" oder vergleichbares Objekt, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">welches 24/7 bewohnt ist. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berufserfahrung:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Berufspraxis im Bereich Objektplanung Gebäude (über die 3 Jahre gemäß Ziffer 1.6.1 der AVB hinausgehend)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ausbildung:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Fach-) Hochschulabschluss (Dipl.-Ingenieur, Master oder vergleichbarer Abschluss) der Fachrichtung Bauingenieurwesen / Architektur
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Angabe Ausbildung (Studium/Fachrichtung), ggf. Zusatzqualifikation</t>
+  </si>
+  <si>
+    <t>Berufspraxis Objektplanung in Jahren nach Ausbildungsabschluss</t>
+  </si>
+  <si>
+    <t>Berufspraxis Objektplanung in Jahren in Projektleitungsfunktion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>davon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mindestens 5 Jahre in Projektleitungsfunktion</t>
+    </r>
+  </si>
+  <si>
+    <t>Weitere Abfragen zur Bewertung jeder einzelnen persönlichen Referenz gemäß A-4 Bewertungsmatrix Angebote, Ziff. 3.1</t>
+  </si>
+  <si>
+    <t>Bieterangaben zu Personal
+hier: Projektleiter*in</t>
+  </si>
+  <si>
+    <t>Referenzbeschreibung liegt als Anlage bei</t>
+  </si>
+  <si>
+    <t>Los-Nummer:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bewertet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>werden Brandschutzmaßnahmen im Hochbau und/oder der Elektro-/Versorgungstechnik.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kriterium 6:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Eigenerklärung, dass das Referenzobjekt eine Strangsanierung beinhaltete.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kriterium 5:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Eigenerklärung, dass das Referenzobjekt Brandschutzmaßnahmen beinhaltete.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Kriterium 4: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Eigenerklärung, das das Referenzobjekt Schadstoffsanierung beinhaltete.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kriterium 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Projektleitungsfunktion Objektplanung Gebäude (Leistungsphasen)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kriterium 2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bauliche Fertigstellung der betreffenden Sanierungs-/Modernisierungsmaßnahme.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bewertet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> wird eine BGF &gt;14.000 m2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bewertet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>wird eine bauliche Fertigstellung nach dem 31.12.2016.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bewertet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>wird die Leistungserbringung aller LP (1 bis 8) HOAI in einer Referenz.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bewertet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>wird eine Schadstoffsanierung mit Schwarzbereich.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bewertet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>wird eine Strangsanierung mit mindestens eine der nachfolgenden Maßnahmen: Trink-/Abwassernetz; Heizleitungsnetz; Lüftungsleitungsnetz</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bauliche Fertigstellung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / sofern noch laufend Angabe Abschluss Lph und vsl. Fertigstellung</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kriterium 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Die betreffende Sanierungs-/Modernisierungsmaßnahme weist eine vergleichbare </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bruttogeschossfläche</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (BGF) auf.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit dem Angebot hat der Bieter für die jeweilige Schlüsselposition Nachweise zu deren persönlicher beruflicher Qualifikation und Erfahrung unter Berücksichtigung der unten aufgeführten Mindeststandards an die Berufserfahrung sowie Mindeststandards an die Wertbarkeit der maßgeblichen persönlichen Referenzen vorzulegen. Neben den vorzunehmenden Angaben zu mindestens zwei persönlichen Referenzen in diesem Formblatt sind die entsprechenden Referenzbeschreibungen, ein tabellarischer Lebenslauf sowie Ausbildungsnachweise vorzulegen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name des anderen Unternehmens, wenn nachfolgend benannte Schlüsselposition Unterauftragnehmer bzw. Mitarbeiter eines Unterauftragnehmers ist  (Sofern zutreffend):
+</t>
+  </si>
+  <si>
+    <t>Ausbildungsnachweise und tabellarischer Lebenslauf liegen als Anlage(n) bei.</t>
+  </si>
+  <si>
+    <t>Angabe BGF in m2 der Sanierungs-/Modernisierungsmaßnahme</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bewertet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> wird eine darüber hinausgehende Berufserfahrung, vgl. A-4 Bewertungsmatrix Angebote, Ziff. 3.1.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Ausbildungsnachweise / tabellarischer Lebenslauf liegen als Anlage(n) bei.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Projekterfahrung:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Vorlage von </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>maximal drei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> persönlichen Referenzen über
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- über Projektleitungsfunktion Objektplanung </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Gebäude </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">mind. der Leistungsphasen 1 bis 8 HOAI (ohne LP 4). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Die Leistungsphasen können über die maximal drei eingereichten wertungsfähigen Referenzen kumuliert nachgewiesen werden.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Bauliche Fertigstellung nicht vor dem 01.01.2012 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>oder noch laufend (bei laufender Baumaßnahme: mindestens Abschluss der Leistungsphase 7 nach HOAI)</t>
+    </r>
+  </si>
+  <si>
+    <t>Referenz 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name des Bieters / Bietergemeinschaft
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bauherr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / Referenzgeber 
+(Name, Anschrift, Kontaktdaten):
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenzbezeichnung
+</t>
+  </si>
+  <si>
+    <t>Ja / Nein:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benannte Person ist Mitarbeiter eines Mitglieds bei einer Bietergemeinschaft bzw. Mitarbeiter eines anderen Unternehmens (Unterauftragnehmer)
+</t>
+  </si>
+  <si>
+    <t>Bewertet wird:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Allgemeine Mindeststandards, die mit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>jeder</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> persönlichen Referenz nachgewiesen werden müssen:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Projekterfahrung:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenzschreiben vom AG liegt als Anlage bei (sofern verfügbar):
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Referenzbeschreibung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> liegt als Anlage bei:
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Anforderungen des Auftraggebers zu 
+technische und berufliche Leistungsfähigkeit
+(2) Anforderungen an das Personal (Schlüsselpositionen) </t>
+  </si>
+  <si>
+    <t>Bieterangabe aus Zeile 18</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angaben des Bieters zu </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verantwortliche*r Planung Technische Ausrüstung</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Das Formblatt ist elektronisch auszufüllen und als </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Excel-Datei </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>zurück zu geben.</t>
+    </r>
+  </si>
+  <si>
+    <t>Verantwortliche*r Planung Technische Ausrüstung</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berufserfahrung:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Berufspraxis im Bereich der </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Technischen Ausrüstung </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(über die 3 Jahre gemäß Ziffer 1.6.1 der AVB DRV-Bund hinausgehend).</t>
+    </r>
+  </si>
+  <si>
+    <t>Weitere Abfragen zur Bewertung gemäß "Bewertungsmatrix Angebote", die in Verbindung mit den allgemeinen Mindeststandards gelten:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Wertung Mindeststandards:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Es werden nur "wertungsfähige" persönliche Referenzen berücksichtigt. Wertungsfähig sind persönliche Referenzen, die die "Allgemeinen Mindeststandards" erfüllen. 
+Nur </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>die</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> persönlichen Referenzen, die die "Allgemeinen Mindeststandards" erfüllen, gehen in die Gesamtbewertung der persönlichen Referenzen ein.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Bewertung / Zuschlagskriterium:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Die Bewertung erfolgt im Zuschlagskriterium 2 "Qualifikation und Erfahrung der als Verantwortlicher Planung Technische Ausrüstung benannten Person" gemäß "Bewertungsmatrix Angebote".
+Dafür werden die Angaben des Bieters  für die Schlüsselposition anhand der jeweiligen Formblätter nebst Nachweisen herangezogen. 
+Zu den persönlichen Referenzen zieht der Auftraggeber </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>maximal eine wertungsfähige persönliche Referenz für die Schlüsselposition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> zur Wertung heran.
+Jede wertungfähige persönliche Referenz wird einzeln bewertet. Liegt mehr als eine wertungsfähige persönliche Referenz vor, geht diejenige mit der höchsten Punktzahl in die Wertung ein.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abschluss der Leistungsphase (LPH) 5 (Datum):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Ggf. getrennt nach Bauabschnitten / Bauteilen - sofern zutreffend.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kriterium 1: Das Referenzobjekt beinhaltete mindestens zwei unterschiedliche Anlagengruppen (mindestens jeweils Honorarzone II) gemäß Anlage 15.2 HOAI. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Kriterium 5: Das Referenzobjekt befand sich während der Bauphase im laufenden Betrieb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Referenzobjekt mit Abschluss der Leistungsphase (LPH) 5 nach HOAI nicht vor dem 01.01.2016 
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kriterium 2: Das Referenzobjekt weist den Abschluss der </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Leistungsphase 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> der Technischen Ausrüstung gemäß HOAI nach dem 31.12.2020 auf.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kriterium 3: Das Referenzobjekt weist den Leistungsumfang </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>der Leistungsphase 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> der Technischen Ausrüstung gemäß HOAI auf.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kriterium 4: Das Referenzobjekt weist den Leistungsumfang </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>der Leistungsphase 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> der Technischen Ausrüstung gemäß HOAI auf.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+Hinweise:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>- In der jeweiligen Referenzbeschreibung werden detaillierte Ausführungen zum Referenzobjekt und dem Leistungszeitraum/-umfang erwartet.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Name des Mitglieds bei BiGe bzw. des anderen Unternehmens (sofern zutreffend):
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angabe Ausbildung (Studium / Fachrichtung), ggf. Zusatzqualifikation:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausbildungsnachweise und tabellarischer Lebenslauf liegen als Anlage bei (Ja / Nein):
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berufspraxis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Technische Ausrüstung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in Jahren </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nach Ausbildung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">sabschluss:
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">- von mindestens 5 Jahren nach Erwerb des Ausbildungsabschlusses, 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name Verantwortliche*r Planung Technische Ausrüstung
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hinweise zu Anforderungen an das Personal (Schlüsselposition)
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Fachplanungsleistungen lt. HOAI § 53 - als Verantwortliche*r Planung Technische Ausrüstung </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mind. der Leistungsphasen 2-5 HOAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (LPH 4 nicht zwingend erforderlich) für ein</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hochbauprojekt mit Sanierungs-/ Modernisierungsmaßnahmen</t>
+    </r>
+  </si>
+  <si>
+    <t>- Das Referenzobjekt Modernisierung / Sanierung beinhaltete mindestens zwei unterschiedliche Anlagengruppen (mindestens jeweils Honorarzone II) gemäß Anlage 15.2 HOAI.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- Sanierung/Modernisierung Ja / Nein: 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">- Honorarzone:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Realisierung innerhalb der Europäischen Union (EU) / der Schweiz
+</t>
+  </si>
+  <si>
+    <t>Bieterangabe aus Zeile 15</t>
+  </si>
+  <si>
+    <t>Bieterangabe aus Zeile 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+'Vorlage von mindestens einer persönlichen Referenz unter Berücksichtigung nachfolgender allgemeiner Mindeststandards:
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angaben zu 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>- aller erbrachten Anlagengruppen:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Angaben zu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- aller erbrachten Leistungsphasen:</t>
+    </r>
+  </si>
+  <si>
+    <t>Angabe Nutzung erneuerbarer Energien, 
+wie z.B.: PV-Anlagen, Wärmepumpen, solarthermische Anlagen, Windkraftanlagen, usw.</t>
+  </si>
+  <si>
+    <t>Kriterium 6: Das Referenzobjekt wurde für einen Auftraggeber im Sinne des § 98 GWB umgesetzt. Es ist ausreichend, wenn der Auftraggeber bei dem Projekt Auftragsvergaben unter Beachtung von für einen Auftraggeber im Sinne des § 98 GWB geltenden Vergabevorschriften durchgeführt hat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kriterium 7: Das Referenzobjekt beinhaltet Technische Ausrüstungs - Systeme, die erneuerbare Energien nutzen.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Anforderungen:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Die Bieter müssen mit ihren Angeboten die Schlüsselposition
+- Verantwortliche*r Planung Technische Ausrüstung
+namentlich benennen und deren/dessen persönliche berufliche Qualifikation, Berufs- und Projekterfahrung (anhand persönlicher Referenzen) unter Berücksichtigung der zu Ausbildung, Berufs- und Projekterfahrung aufgestellten Mindeststandards nachweisen.
+Dafür ist das ausgefüllte Formblatt "Anforderung-Angaben Personal" zur Schlüsselposition nebst: 
+- Ausbildungsnachweisen,
+- tabellarischer Lebenslauf, 
+- Angaben zu mindestens einer persönlichen Referenz über </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Leistungen der Technischen Ausrüstung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> aus den letzten 10 Jahren sowie entsprechende aussagefähige Referenzbeschreibungen (nach eigenem Format)
+vorzulegen.
+Die Mindeststandards sind dem Formblatt zu entnehmen.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Sofern die vorgelegten Nachweise zur Schlüsselposition die jeweils aufgestellten Mindeststandards hinsichtlich der Ausbildung, Berufs- und Projekterfahrung nicht erfüllen, wird das Angebot ausgeschlossen.
+Demnach müssen die allgemeinen Mindeststandards (Zeilen 13 bis 18 im Formblatt "A-6_Anforderungen_Angaben_Personal") mit jeder persönlichen Referenz nachgewiesen werden.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ausbildung:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Fach-) Hochschulabschluss (Dipl.-Ing. / Master / Bachelor) in der Fachrichtung Technische Ausrüstung; Maschinenbau mit Schwerpunkt TGA, Versorgungstechnik, Technische Gebäudeausrüstung, Gebäudetechnik, Energietechnik, HKLS oder Elektrotechnik/ Elektrotech. Gebäudeausrüstung.</t>
+    </r>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1421,7 +2698,7 @@
       </c>
       <c r="C5" s="116" t="inlineStr">
         <is>
-          <t>Diplom-Ingenieur (FH), Versorgungstechnik, Hochschule Bremen; Zusatzqualifikationen: Energieeffiziente Nichtwohngebäude, Fachplaner Brandschutztechnische Schnittstellenkoordination</t>
+          <t>Diplom-Ingenieur (FH), Versorgungstechnik, Hochschule Bremen; Zertifikatslehrgang Energieeffiziente Nichtwohngebäude; Fachplaner Brandschutztechnische Schnittstellenkoordination</t>
         </is>
       </c>
       <c r="D5" s="141" t="n"/>
@@ -1490,7 +2767,7 @@
       </c>
       <c r="C9" s="76" t="inlineStr">
         <is>
-          <t>Referenz 1</t>
+          <t>TA-1</t>
         </is>
       </c>
       <c r="D9" s="77" t="inlineStr">
@@ -1519,11 +2796,6 @@
 </t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sanierung und Umbau Klinikgebäude Haus C</t>
-        </is>
-      </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
           <t>Schulcampus Nord</t>
@@ -1546,17 +2818,17 @@
       </c>
       <c r="C11" s="116" t="inlineStr">
         <is>
-          <t>Universitätsklinikum Schleswig-Holstein AöR, Campus Lübeck, Ratzeburger Allee 160, 23538 Lübeck</t>
+          <t>Universitätsklinikum Schleswig-Holstein AöR</t>
         </is>
       </c>
       <c r="D11" s="116" t="inlineStr">
         <is>
-          <t>SBH | Schulbau Hamburg, An der Stadthausbrücke 1, 20355 Hamburg</t>
+          <t>SBH | Schulbau Hamburg</t>
         </is>
       </c>
       <c r="E11" s="116" t="inlineStr">
         <is>
-          <t>Hamburg Port Authority AöR, Neuer Wandrahm 4, 20457 Hamburg</t>
+          <t>Hamburg Port Authority AöR</t>
         </is>
       </c>
       <c r="F11" s="56" t="n"/>
@@ -1586,17 +2858,17 @@
       </c>
       <c r="C13" s="116" t="inlineStr">
         <is>
-          <t>LPH 2, 3, 5, 6, 8</t>
+          <t>2, 3, 5, 6, 8</t>
         </is>
       </c>
       <c r="D13" s="116" t="inlineStr">
         <is>
-          <t>LPH 2, 3, 5, 6, 8</t>
+          <t>2, 3, 5, 6, 8</t>
         </is>
       </c>
       <c r="E13" s="116" t="inlineStr">
         <is>
-          <t>LPH 2, 3, 5, 6, 8</t>
+          <t>2, 3, 5, 6, 8</t>
         </is>
       </c>
     </row>
@@ -1620,7 +2892,7 @@
       </c>
       <c r="E14" s="116" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -1690,12 +2962,12 @@
       </c>
       <c r="C17" s="116" t="inlineStr">
         <is>
-          <t>Lübeck, Deutschland</t>
+          <t>Lübeck, Germany</t>
         </is>
       </c>
       <c r="D17" s="116" t="inlineStr">
         <is>
-          <t>Hamburg, Deutschland</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="E17" s="116" t="inlineStr">
@@ -1719,7 +2991,7 @@
       </c>
       <c r="C18" s="116" t="inlineStr">
         <is>
-          <t>February 2024</t>
+          <t>Februar 2024</t>
         </is>
       </c>
       <c r="D18" s="72" t="inlineStr">
@@ -1729,7 +3001,7 @@
       </c>
       <c r="E18" s="116" t="inlineStr">
         <is>
-          <t>June 2019</t>
+          <t>Juni 2019</t>
         </is>
       </c>
     </row>
@@ -18252,7 +19524,7 @@
       </c>
       <c r="E24" s="116" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -18279,7 +19551,7 @@
       </c>
       <c r="E25" s="116" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -18298,17 +19570,17 @@
       </c>
       <c r="C26" s="116" t="inlineStr">
         <is>
-          <t>Geothermie (Wärmepumpe)</t>
+          <t>Geothermal-supported heat pump system</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Photovoltaik</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E26" s="116" t="inlineStr">
         <is>
-          <t>Photovoltaik</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="H26" s="48" t="n"/>
@@ -34711,7 +35983,7 @@
       </c>
       <c r="E27" s="116" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -34727,21 +35999,9 @@
           <t>Ja / Nein:</t>
         </is>
       </c>
-      <c r="C28" s="116" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="D28" s="116" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E28" s="116" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
+      <c r="C28" s="116" t="n"/>
+      <c r="D28" s="116" t="n"/>
+      <c r="E28" s="116" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="108" t="n"/>
@@ -35354,4 +36614,280 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ESLAddDocumentID xmlns="0242f6e2-51a6-4263-8f69-32f0f5e328da">NotAdded</ESLAddDocumentID>
+    <_dlc_DocId xmlns="0242f6e2-51a6-4263-8f69-32f0f5e328da">M1526029-6996-295</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="0242f6e2-51a6-4263-8f69-32f0f5e328da">
+      <Url>https://esl.deiapps.kpmg.com/matters/1526029/_layouts/15/DocIdRedir.aspx?ID=M1526029-6996-295</Url>
+      <Description>M1526029-6996-295</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010060DE0FDF3202B745B8C704AF18242F60" ma:contentTypeVersion="2" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="c56d09adc90c6265cde94291fd4e4183">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0242f6e2-51a6-4263-8f69-32f0f5e328da" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2cc216f0d94e2d4be971c39e2c19bc3a" ns2:_="">
+    <xsd:import namespace="0242f6e2-51a6-4263-8f69-32f0f5e328da"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:_dlc_DocId" minOccurs="0"/>
+                <xsd:element ref="ns2:_dlc_DocIdUrl" minOccurs="0"/>
+                <xsd:element ref="ns2:_dlc_DocIdPersistId" minOccurs="0"/>
+                <xsd:element ref="ns2:ESLAddDocumentID" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0242f6e2-51a6-4263-8f69-32f0f5e328da" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Wert der Dokument-ID" ma:description="Der Wert der diesem Element zugewiesenen Dokument-ID." ma:internalName="_dlc_DocId" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Dokument-ID" ma:description="Permanenter Hyperlink zu diesem Dokument." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:URL">
+            <xsd:sequence>
+              <xsd:element name="Url" type="dms:ValidUrl" minOccurs="0" nillable="true"/>
+              <xsd:element name="Description" type="xsd:string" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="_dlc_DocIdPersistId" ma:index="10" nillable="true" ma:displayName="Beständige ID" ma:description="ID beim Hinzufügen beibehalten." ma:hidden="true" ma:internalName="_dlc_DocIdPersistId" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ESLAddDocumentID" ma:index="11" nillable="true" ma:displayName="DocID" ma:default="NotAdded" ma:format="Dropdown" ma:internalName="ESLAddDocumentID" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Added"/>
+          <xsd:enumeration value="NotAdded"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81908455-EEB9-4DE9-9F30-E978B78AF8AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0242f6e2-51a6-4263-8f69-32f0f5e328da"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7DBE66-213F-4B10-AB6A-504D64CEFB9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0242f6e2-51a6-4263-8f69-32f0f5e328da"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81C9855A-FE15-42E0-A781-107004B62257}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF34414-5D80-40DF-B908-8872768B6ABC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tables_filled/22b5da6f-d542-421f-b00b-8d360f06d0b0.xlsx
+++ b/tables_filled/22b5da6f-d542-421f-b00b-8d360f06d0b0.xlsx
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C9" s="76" t="inlineStr">
         <is>
-          <t>TA-1</t>
+          <t>Referenz 1</t>
         </is>
       </c>
       <c r="D9" s="77" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="C11" s="116" t="inlineStr">
         <is>
-          <t>Universitätsklinikum Schleswig-Holstein AöR</t>
+          <t>Sanierung und Umbau Klinikgebäude Haus C, Universitätsklinikum Schleswig-Holstein AöR</t>
         </is>
       </c>
       <c r="D11" s="116" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E14" s="116" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E17" s="116" t="inlineStr">
         <is>
-          <t>Hamburg, Deutschland</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C18" s="116" t="inlineStr">
         <is>
-          <t>Februar 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="D18" s="72" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E18" s="116" t="inlineStr">
         <is>
-          <t>Juni 2019</t>
+          <t>June 2019</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="E24" s="116" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="E25" s="116" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
@@ -35983,7 +35983,7 @@
       </c>
       <c r="E27" s="116" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
